--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/NEBRASKA_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/NEBRASKA_2010.xlsx
@@ -1680,7 +1680,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C74">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C105">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C129">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C631">
